--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Migration/BIBS_Migration_BRD-13_Cutover_Task_Plan_v1.2.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Migration/BIBS_Migration_BRD-13_Cutover_Task_Plan_v1.2.xlsx
@@ -4931,7 +4931,7 @@
       <c r="D16" s="12" t="inlineStr"/>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Legacy clean-up drives - UPP with no reference, invoices open more than 5 years, duplicate clients flagged in Mock 3, unmapped codes</t>
+          <t>Legacy clean-up drives - UPP with no reference, invoices open more than 5 years, duplicate clients flagged in Trial migration 3, unmapped codes</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -4945,7 +4945,7 @@
       <c r="H16" s="12" t="inlineStr"/>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Clean-up tracker; counts reduced against Mock 3 profiling</t>
+          <t>Clean-up tracker; counts reduced against Trial migration 3 profiling</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       <c r="D17" s="12" t="inlineStr"/>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Renewal processing team ready for the January expiries - staffing plan for January (handlers, overtime, back-up) signed; BIBS Renewal training completed; day-1 priority queue worked on the Mock 4 and dress-rehearsal data; draft RA-sent file from the Excel trackers validated and its rejects reviewed (maker-checker)</t>
+          <t>Renewal processing team ready for the January expiries - staffing plan for January (handlers, overtime, back-up) signed; BIBS Renewal training completed; day-1 priority queue worked on the Trial migration 4 and dress-rehearsal data; draft RA-sent file from the Excel trackers validated and its rejects reviewed (maker-checker)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Files CHECKED; counts against the Mock 4 volumes within 5 percent</t>
+          <t>Files CHECKED; counts against the Trial migration 4 volumes within 5 percent</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr"/>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Within 2 business days - root cause, new go-live date, which mocks to repeat; purge the production staging of the failed cutover within 5 days.</t>
+          <t>Within 2 business days - root cause, new go-live date, which trial migrations to repeat; purge the production staging of the failed cutover within 5 days.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
